--- a/SGC-CKN/Excel/21b0d61f-eae4-49d0-8517-1ddc505d6e2c_Lô_CT-02_P7-34_D800_22-03-2026.xlsx
+++ b/SGC-CKN/Excel/21b0d61f-eae4-49d0-8517-1ddc505d6e2c_Lô_CT-02_P7-34_D800_22-03-2026.xlsx
@@ -102,7 +102,7 @@
 22/03/2026</t>
   </si>
   <si>
-    <t xml:space="preserve">18:20
+    <t xml:space="preserve">18:00
 22/03/2026</t>
   </si>
   <si>
@@ -115,7 +115,7 @@
     <t>Cát pha xám ghi, xám nâu TT dẻo</t>
   </si>
   <si>
-    <t xml:space="preserve">18:50
+    <t xml:space="preserve">18:10
 22/03/2026</t>
   </si>
   <si>
@@ -368,11 +368,6 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF7ED"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor rgb="FFA7F3D0"/>
       </patternFill>
     </fill>
@@ -384,6 +379,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFDDD6FE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF7ED"/>
       </patternFill>
     </fill>
     <fill>
@@ -539,35 +539,35 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="10" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="11" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="12" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1206,19 +1206,19 @@
         <v>29</v>
       </c>
       <c r="F11" s="5">
-        <v>-3.46</v>
+        <v>0</v>
       </c>
       <c r="G11" s="5">
-        <v>-10.61</v>
+        <v>-7.5</v>
       </c>
       <c r="H11" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I11" s="5">
-        <v>7.15</v>
+        <v>7.5</v>
       </c>
       <c r="J11" s="8">
-        <v>14.3</v>
+        <v>45</v>
       </c>
       <c r="K11" s="6" t="s">
         <v>30</v>
@@ -1241,126 +1241,126 @@
         <v>33</v>
       </c>
       <c r="F12" s="9">
-        <v>-10.61</v>
+        <v>-7.5</v>
       </c>
       <c r="G12" s="9">
-        <v>-11.71</v>
+        <v>-9.2</v>
       </c>
       <c r="H12" s="9">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="I12" s="9">
-        <v>1.1</v>
-      </c>
-      <c r="J12" s="12">
-        <v>2.2</v>
+        <v>1.7</v>
+      </c>
+      <c r="J12" s="8">
+        <v>10.2</v>
       </c>
       <c r="K12" s="10" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="13" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A13" s="13" t="s">
+      <c r="A13" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="B13" s="13" t="s">
+      <c r="B13" s="12" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="13" t="s">
         <v>35</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D13" s="14" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E13" s="14" t="s">
         <v>36</v>
       </c>
-      <c r="F13" s="13">
-        <v>-11.71</v>
-      </c>
-      <c r="G13" s="13">
-        <v>-17.41</v>
-      </c>
-      <c r="H13" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="I13" s="13">
-        <v>5.7</v>
+      <c r="F13" s="12">
+        <v>-9.2</v>
+      </c>
+      <c r="G13" s="12">
+        <v>-17.4</v>
+      </c>
+      <c r="H13" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="I13" s="12">
+        <v>8.2</v>
       </c>
       <c r="J13" s="8">
-        <v>68.4</v>
-      </c>
-      <c r="K13" s="14" t="s">
+        <v>10.93</v>
+      </c>
+      <c r="K13" s="13" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="14" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A14" s="16" t="s">
+      <c r="A14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="B14" s="16" t="s">
+      <c r="B14" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="17" t="s">
+      <c r="C14" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="D14" s="18" t="s">
+      <c r="D14" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="E14" s="18" t="s">
+      <c r="E14" s="17" t="s">
         <v>39</v>
       </c>
-      <c r="F14" s="16">
-        <v>-17.41</v>
-      </c>
-      <c r="G14" s="16">
+      <c r="F14" s="15">
+        <v>-17.4</v>
+      </c>
+      <c r="G14" s="15">
         <v>-24.65</v>
       </c>
-      <c r="H14" s="16">
+      <c r="H14" s="15">
         <v>0.25</v>
       </c>
-      <c r="I14" s="16">
-        <v>7.24</v>
+      <c r="I14" s="15">
+        <v>7.25</v>
       </c>
       <c r="J14" s="8">
-        <v>28.96</v>
-      </c>
-      <c r="K14" s="17" t="s">
+        <v>29</v>
+      </c>
+      <c r="K14" s="16" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="15" ht="36" customHeight="1" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A15" s="19" t="s">
+      <c r="A15" s="18" t="s">
         <v>40</v>
       </c>
-      <c r="B15" s="19" t="s">
+      <c r="B15" s="18" t="s">
         <v>11</v>
       </c>
-      <c r="C15" s="20" t="s">
+      <c r="C15" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="21" t="s">
+      <c r="D15" s="20" t="s">
         <v>39</v>
       </c>
-      <c r="E15" s="21" t="s">
+      <c r="E15" s="20" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19">
+      <c r="F15" s="18">
         <v>-24.65</v>
       </c>
-      <c r="G15" s="19">
+      <c r="G15" s="18">
         <v>-25.85</v>
       </c>
-      <c r="H15" s="19">
+      <c r="H15" s="18">
         <v>0.5</v>
       </c>
-      <c r="I15" s="19">
+      <c r="I15" s="18">
         <v>1.2</v>
       </c>
-      <c r="J15" s="12">
+      <c r="J15" s="21">
         <v>2.4</v>
       </c>
-      <c r="K15" s="20" t="s">
+      <c r="K15" s="19" t="s">
         <v>30</v>
       </c>
     </row>
@@ -1384,16 +1384,16 @@
         <v>-25.85</v>
       </c>
       <c r="G16" s="22">
-        <v>-35.08</v>
+        <v>-35.98</v>
       </c>
       <c r="H16" s="22">
         <v>1.42</v>
       </c>
       <c r="I16" s="22">
-        <v>9.23</v>
+        <v>10.13</v>
       </c>
       <c r="J16" s="8">
-        <v>6.52</v>
+        <v>7.15</v>
       </c>
       <c r="K16" s="23" t="s">
         <v>30</v>
@@ -1416,7 +1416,7 @@
         <v>48</v>
       </c>
       <c r="F17" s="25">
-        <v>-35.08</v>
+        <v>-35.98</v>
       </c>
       <c r="G17" s="25">
         <v>-38.1</v>
@@ -1425,10 +1425,10 @@
         <v>0.58</v>
       </c>
       <c r="I17" s="25">
-        <v>3.02</v>
-      </c>
-      <c r="J17" s="8">
-        <v>5.18</v>
+        <v>2.12</v>
+      </c>
+      <c r="J17" s="21">
+        <v>3.63</v>
       </c>
       <c r="K17" s="26" t="s">
         <v>30</v>
@@ -1462,7 +1462,7 @@
       <c r="I18" s="28">
         <v>1.5</v>
       </c>
-      <c r="J18" s="12">
+      <c r="J18" s="21">
         <v>4.5</v>
       </c>
       <c r="K18" s="29" t="s">
@@ -1489,7 +1489,7 @@
         <v>-39.6</v>
       </c>
       <c r="G19" s="31">
-        <v>-43.87</v>
+        <v>-43.870000000000005</v>
       </c>
       <c r="H19" s="31">
         <v>0.92</v>
@@ -1497,7 +1497,7 @@
       <c r="I19" s="31">
         <v>4.27</v>
       </c>
-      <c r="J19" s="12">
+      <c r="J19" s="21">
         <v>4.66</v>
       </c>
       <c r="K19" s="32" t="s">
@@ -1521,19 +1521,19 @@
         <v>58</v>
       </c>
       <c r="F20" s="34">
-        <v>-43.87</v>
+        <v>-43.870000000000005</v>
       </c>
       <c r="G20" s="34">
-        <v>-44.88</v>
+        <v>-44.830000000000005</v>
       </c>
       <c r="H20" s="34">
         <v>0.25</v>
       </c>
       <c r="I20" s="34">
-        <v>1.01</v>
-      </c>
-      <c r="J20" s="12">
-        <v>4.04</v>
+        <v>0.96</v>
+      </c>
+      <c r="J20" s="21">
+        <v>3.84</v>
       </c>
       <c r="K20" s="35" t="s">
         <v>30</v>
@@ -1688,19 +1688,19 @@
         <v>1</v>
       </c>
       <c r="E2" s="5">
-        <v>-3.46</v>
+        <v>0</v>
       </c>
       <c r="F2" s="5">
-        <v>-10.61</v>
+        <v>-7.5</v>
       </c>
       <c r="G2" s="5">
-        <v>0.5</v>
+        <v>0.17</v>
       </c>
       <c r="H2" s="5">
-        <v>7.15</v>
+        <v>7.5</v>
       </c>
       <c r="I2" s="8">
-        <v>14.3</v>
+        <v>45</v>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1717,105 +1717,105 @@
         <v>1</v>
       </c>
       <c r="E3" s="9">
-        <v>-10.61</v>
+        <v>-7.5</v>
       </c>
       <c r="F3" s="9">
-        <v>-11.71</v>
+        <v>-9.2</v>
       </c>
       <c r="G3" s="9">
+        <v>0.17</v>
+      </c>
+      <c r="H3" s="9">
+        <v>1.7</v>
+      </c>
+      <c r="I3" s="8">
+        <v>10.2</v>
+      </c>
+    </row>
+    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A4" s="12">
+        <v>3</v>
+      </c>
+      <c r="B4" s="12" t="s">
+        <v>11</v>
+      </c>
+      <c r="C4" s="13" t="s">
+        <v>35</v>
+      </c>
+      <c r="D4" s="12">
+        <v>1</v>
+      </c>
+      <c r="E4" s="12">
+        <v>-9.2</v>
+      </c>
+      <c r="F4" s="12">
+        <v>-17.4</v>
+      </c>
+      <c r="G4" s="12">
+        <v>0.75</v>
+      </c>
+      <c r="H4" s="12">
+        <v>8.2</v>
+      </c>
+      <c r="I4" s="8">
+        <v>10.93</v>
+      </c>
+    </row>
+    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A5" s="15">
+        <v>4</v>
+      </c>
+      <c r="B5" s="15" t="s">
+        <v>11</v>
+      </c>
+      <c r="C5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="15">
+        <v>1</v>
+      </c>
+      <c r="E5" s="15">
+        <v>-17.4</v>
+      </c>
+      <c r="F5" s="15">
+        <v>-24.65</v>
+      </c>
+      <c r="G5" s="15">
+        <v>0.25</v>
+      </c>
+      <c r="H5" s="15">
+        <v>7.25</v>
+      </c>
+      <c r="I5" s="8">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A6" s="18">
+        <v>5</v>
+      </c>
+      <c r="B6" s="18" t="s">
+        <v>11</v>
+      </c>
+      <c r="C6" s="19" t="s">
+        <v>41</v>
+      </c>
+      <c r="D6" s="18">
+        <v>1</v>
+      </c>
+      <c r="E6" s="18">
+        <v>-24.65</v>
+      </c>
+      <c r="F6" s="18">
+        <v>-25.85</v>
+      </c>
+      <c r="G6" s="18">
         <v>0.5</v>
       </c>
-      <c r="H3" s="9">
-        <v>1.1</v>
-      </c>
-      <c r="I3" s="12">
-        <v>2.2</v>
-      </c>
-    </row>
-    <row r="4" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A4" s="13">
-        <v>3</v>
-      </c>
-      <c r="B4" s="13" t="s">
-        <v>11</v>
-      </c>
-      <c r="C4" s="14" t="s">
-        <v>35</v>
-      </c>
-      <c r="D4" s="13">
-        <v>1</v>
-      </c>
-      <c r="E4" s="13">
-        <v>-11.71</v>
-      </c>
-      <c r="F4" s="13">
-        <v>-17.41</v>
-      </c>
-      <c r="G4" s="13">
-        <v>0.08</v>
-      </c>
-      <c r="H4" s="13">
-        <v>5.7</v>
-      </c>
-      <c r="I4" s="8">
-        <v>68.4</v>
-      </c>
-    </row>
-    <row r="5" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A5" s="16">
-        <v>4</v>
-      </c>
-      <c r="B5" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="C5" s="17" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="16">
-        <v>1</v>
-      </c>
-      <c r="E5" s="16">
-        <v>-17.41</v>
-      </c>
-      <c r="F5" s="16">
-        <v>-24.65</v>
-      </c>
-      <c r="G5" s="16">
-        <v>0.25</v>
-      </c>
-      <c r="H5" s="16">
-        <v>7.24</v>
-      </c>
-      <c r="I5" s="8">
-        <v>28.96</v>
-      </c>
-    </row>
-    <row r="6" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
-      <c r="A6" s="19">
-        <v>5</v>
-      </c>
-      <c r="B6" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="C6" s="20" t="s">
-        <v>41</v>
-      </c>
-      <c r="D6" s="19">
-        <v>1</v>
-      </c>
-      <c r="E6" s="19">
-        <v>-24.65</v>
-      </c>
-      <c r="F6" s="19">
-        <v>-25.85</v>
-      </c>
-      <c r="G6" s="19">
-        <v>0.5</v>
-      </c>
-      <c r="H6" s="19">
+      <c r="H6" s="18">
         <v>1.2</v>
       </c>
-      <c r="I6" s="12">
+      <c r="I6" s="21">
         <v>2.4</v>
       </c>
     </row>
@@ -1836,16 +1836,16 @@
         <v>-25.85</v>
       </c>
       <c r="F7" s="22">
-        <v>-35.08</v>
+        <v>-35.98</v>
       </c>
       <c r="G7" s="22">
         <v>1.42</v>
       </c>
       <c r="H7" s="22">
-        <v>9.23</v>
+        <v>10.13</v>
       </c>
       <c r="I7" s="8">
-        <v>6.52</v>
+        <v>7.15</v>
       </c>
     </row>
     <row r="8" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1862,7 +1862,7 @@
         <v>1</v>
       </c>
       <c r="E8" s="25">
-        <v>-35.08</v>
+        <v>-35.98</v>
       </c>
       <c r="F8" s="25">
         <v>-38.1</v>
@@ -1871,10 +1871,10 @@
         <v>0.58</v>
       </c>
       <c r="H8" s="25">
-        <v>3.02</v>
-      </c>
-      <c r="I8" s="8">
-        <v>5.18</v>
+        <v>2.12</v>
+      </c>
+      <c r="I8" s="21">
+        <v>3.63</v>
       </c>
     </row>
     <row r="9" ht="32" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1902,7 +1902,7 @@
       <c r="H9" s="28">
         <v>1.5</v>
       </c>
-      <c r="I9" s="12">
+      <c r="I9" s="21">
         <v>4.5</v>
       </c>
     </row>
@@ -1931,7 +1931,7 @@
       <c r="H10" s="31">
         <v>4.27</v>
       </c>
-      <c r="I10" s="12">
+      <c r="I10" s="21">
         <v>4.66</v>
       </c>
     </row>
@@ -1952,16 +1952,16 @@
         <v>-43.87</v>
       </c>
       <c r="F11" s="34">
-        <v>-44.88</v>
+        <v>-44.83</v>
       </c>
       <c r="G11" s="34">
         <v>0.25</v>
       </c>
       <c r="H11" s="34">
-        <v>1.01</v>
-      </c>
-      <c r="I11" s="12">
-        <v>4.04</v>
+        <v>0.96</v>
+      </c>
+      <c r="I11" s="21">
+        <v>3.84</v>
       </c>
     </row>
     <row r="12" ht="28" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
@@ -1978,19 +1978,19 @@
         <v>10</v>
       </c>
       <c r="E12" s="39">
-        <v>-3.46</v>
+        <v>0</v>
       </c>
       <c r="F12" s="39">
-        <v>-44.88</v>
+        <v>-44.83</v>
       </c>
       <c r="G12" s="39">
         <v>5.33</v>
       </c>
       <c r="H12" s="39">
-        <v>41.42</v>
+        <v>44.83</v>
       </c>
       <c r="I12" s="39">
-        <v>7.77</v>
+        <v>8.41</v>
       </c>
     </row>
   </sheetData>
